--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/nov-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/nov-2025.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>484450.95</v>
+        <v>481726.08</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8134.41</v>
+        <v>8050.32</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12269.22</v>
+        <v>12200.9</v>
       </c>
     </row>
     <row r="5">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9554.700000000001</v>
+        <v>9449.709999999999</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1721.57</v>
+        <v>1712.4</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7015.39</v>
+        <v>7049.15</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8952.15</v>
+        <v>9018.08</v>
       </c>
     </row>
     <row r="9">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>111557.59</v>
+        <v>112379.21</v>
       </c>
     </row>
     <row r="10">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6283.72</v>
+        <v>6274.95</v>
       </c>
     </row>
     <row r="11">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>32064.2</v>
+        <v>32019.45</v>
       </c>
     </row>
     <row r="12">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9554.700000000001</v>
+        <v>9605.530000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>9554.700000000001</v>
+        <v>9605.530000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/nov-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/nov-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/nov-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/nov-2025.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/nov-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/nov-2025.xlsx
@@ -627,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -688,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -749,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -810,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +887,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +952,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1058,7 +1082,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1119,7 +1147,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1180,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1241,7 +1277,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
